--- a/main/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="180">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -424,6 +424,9 @@
   </si>
   <si>
     <t>Forme galénique du produit de santé. EDQM Standard Terms (0.4.0.127.0.16.1.1.2.1) / classe PDF (forme galénique).</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>EDQM Standard Terms</t>
@@ -2491,10 +2494,10 @@
         <v>73</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Z16" t="s" s="2">
         <v>73</v>
@@ -2532,10 +2535,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2561,10 +2564,10 @@
         <v>123</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2615,7 +2618,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>83</v>
@@ -2632,10 +2635,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2658,13 +2661,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2715,7 +2718,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2732,10 +2735,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2761,10 +2764,10 @@
         <v>79</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2791,10 +2794,10 @@
         <v>73</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Z19" t="s" s="2">
         <v>73</v>
@@ -2815,7 +2818,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>83</v>
@@ -2832,10 +2835,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2861,10 +2864,10 @@
         <v>123</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2915,7 +2918,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2932,10 +2935,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2958,13 +2961,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3015,7 +3018,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>83</v>
@@ -3032,10 +3035,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3061,10 +3064,10 @@
         <v>79</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3115,7 +3118,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3132,10 +3135,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3161,10 +3164,10 @@
         <v>79</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3215,7 +3218,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3232,10 +3235,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3258,13 +3261,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3315,7 +3318,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3332,10 +3335,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3358,13 +3361,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3415,7 +3418,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3432,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3461,10 +3464,10 @@
         <v>79</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3515,7 +3518,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3532,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3561,10 +3564,10 @@
         <v>123</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3615,7 +3618,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3632,10 +3635,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3658,13 +3661,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3715,7 +3718,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -3732,10 +3735,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3758,13 +3761,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3815,7 +3818,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -3832,10 +3835,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3861,10 +3864,10 @@
         <v>123</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3915,7 +3918,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3932,10 +3935,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3961,10 +3964,10 @@
         <v>79</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4015,7 +4018,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -4032,10 +4035,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4058,13 +4061,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4115,7 +4118,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4132,10 +4135,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4161,10 +4164,10 @@
         <v>123</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4215,7 +4218,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4232,10 +4235,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4261,10 +4264,10 @@
         <v>84</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4315,7 +4318,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4332,10 +4335,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4358,13 +4361,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4415,7 +4418,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
